--- a/activity/M01A09/M01A09_TaludRef.xlsx
+++ b/activity/M01A09/M01A09_TaludRef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C869D620-A41D-40F7-9825-7D6CCDA8F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F526E-5364-4C44-A4DF-B38D2C619A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="35">
   <si>
     <t>Observaciones</t>
   </si>
@@ -101,9 +101,6 @@
     <t>M01A09</t>
   </si>
   <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A09/Readme.md</t>
-  </si>
-  <si>
     <t>Grupo 6</t>
   </si>
   <si>
@@ -158,7 +155,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +232,12 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -250,7 +253,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -420,15 +423,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -582,32 +576,11 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -632,29 +605,50 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2060,25 +2054,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
@@ -2101,14 +2095,14 @@
       <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="28">
         <v>5</v>
       </c>
       <c r="D5" s="22">
         <f>Detalle!C14*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="37"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="24">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2118,14 +2112,14 @@
       <c r="B6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="28">
         <v>5</v>
       </c>
       <c r="D6" s="22">
         <f>Detalle!F14*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="37"/>
+      <c r="E6" s="30"/>
       <c r="F6" s="24">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2135,14 +2129,14 @@
       <c r="B7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="28">
         <v>5</v>
       </c>
       <c r="D7" s="22">
         <f>Detalle!I14*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="37"/>
+      <c r="E7" s="30"/>
       <c r="F7" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2152,14 +2146,14 @@
       <c r="B8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="28">
         <v>5</v>
       </c>
       <c r="D8" s="22">
         <f>Detalle!L14*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="37"/>
+      <c r="E8" s="30"/>
       <c r="F8" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2169,14 +2163,14 @@
       <c r="B9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="28">
         <v>5</v>
       </c>
       <c r="D9" s="22">
         <f>Detalle!O14*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="37"/>
+      <c r="E9" s="30"/>
       <c r="F9" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2184,16 +2178,16 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="35">
+        <v>20</v>
+      </c>
+      <c r="C10" s="28">
         <v>5</v>
       </c>
       <c r="D10" s="22">
         <f>Detalle!R14*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="37"/>
+      <c r="E10" s="30"/>
       <c r="F10" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2201,16 +2195,16 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="35">
+        <v>21</v>
+      </c>
+      <c r="C11" s="28">
         <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>Detalle!U14*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="37"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2218,16 +2212,16 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="35">
+        <v>22</v>
+      </c>
+      <c r="C12" s="28">
         <v>5</v>
       </c>
       <c r="D12" s="22">
         <f>Detalle!X14*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="37"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2235,16 +2229,16 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="35">
+        <v>23</v>
+      </c>
+      <c r="C13" s="28">
         <v>5</v>
       </c>
       <c r="D13" s="22">
         <f>Detalle!AA14*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="37"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2252,16 +2246,16 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="35">
+        <v>24</v>
+      </c>
+      <c r="C14" s="28">
         <v>5</v>
       </c>
       <c r="D14" s="22">
         <f>Detalle!AD14*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="37"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2269,16 +2263,16 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="35">
+        <v>25</v>
+      </c>
+      <c r="C15" s="28">
         <v>5</v>
       </c>
       <c r="D15" s="22">
         <f>Detalle!AG14*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="37"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2286,16 +2280,16 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="35">
+        <v>26</v>
+      </c>
+      <c r="C16" s="28">
         <v>5</v>
       </c>
       <c r="D16" s="22">
         <f>Detalle!AJ14*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="37"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2303,16 +2297,16 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="35">
+        <v>27</v>
+      </c>
+      <c r="C17" s="28">
         <v>5</v>
       </c>
       <c r="D17" s="22">
         <f>Detalle!AM14*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="37"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2320,56 +2314,55 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="36">
+        <v>28</v>
+      </c>
+      <c r="C18" s="29">
         <v>5</v>
       </c>
       <c r="D18" s="23">
         <f>Detalle!AP14*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="38"/>
+      <c r="E18" s="31"/>
       <c r="F18" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
+      <c r="B19" s="48" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A09 en GitHub.</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{4FDBDA31-2000-41CC-B404-5C86FF7256E2}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2449,96 +2442,96 @@
     </row>
     <row r="2" spans="1:44" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="27" t="str">
+      <c r="C2" s="43" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="27" t="str">
+      <c r="D2" s="44"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="43" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="27" t="str">
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="43" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="27" t="str">
+      <c r="J2" s="44"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="43" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="27" t="str">
+      <c r="M2" s="44"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="43" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="27" t="str">
+      <c r="P2" s="44"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="43" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="28"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="27" t="str">
+      <c r="S2" s="44"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="43" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="28"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="27" t="str">
+      <c r="V2" s="44"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="43" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="27" t="str">
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="43" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="27" t="str">
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="43" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="27" t="str">
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="43" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="27" t="str">
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="43" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="27" t="str">
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="43" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="27" t="str">
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="43" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="29"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="45"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="31"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2670,615 +2663,615 @@
       <c r="B4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="39"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="39"/>
-      <c r="AB4" s="40"/>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="40"/>
-      <c r="AF4" s="41"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="40"/>
-      <c r="AI4" s="41"/>
-      <c r="AJ4" s="39"/>
-      <c r="AK4" s="40"/>
-      <c r="AL4" s="41"/>
-      <c r="AM4" s="39"/>
-      <c r="AN4" s="40"/>
-      <c r="AO4" s="41"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="40"/>
-      <c r="AR4" s="41"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="33"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="33"/>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="33"/>
+      <c r="AR4" s="34"/>
     </row>
     <row r="5" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B5" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="39">
-        <v>0</v>
-      </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="39">
-        <v>0</v>
-      </c>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="39">
-        <v>0</v>
-      </c>
-      <c r="J5" s="40"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="39">
-        <v>0</v>
-      </c>
-      <c r="M5" s="40"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="39">
-        <v>0</v>
-      </c>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="39">
-        <v>0</v>
-      </c>
-      <c r="S5" s="40"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="39">
-        <v>0</v>
-      </c>
-      <c r="V5" s="40"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="39">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="40"/>
-      <c r="AC5" s="41"/>
-      <c r="AD5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="40"/>
-      <c r="AL5" s="41"/>
-      <c r="AM5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="40"/>
-      <c r="AO5" s="41"/>
-      <c r="AP5" s="39">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="40"/>
-      <c r="AR5" s="41"/>
+        <v>30</v>
+      </c>
+      <c r="C5" s="32">
+        <v>0</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="32">
+        <v>0</v>
+      </c>
+      <c r="G5" s="33"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="32">
+        <v>0</v>
+      </c>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="32">
+        <v>0</v>
+      </c>
+      <c r="M5" s="33"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="32">
+        <v>0</v>
+      </c>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="32">
+        <v>0</v>
+      </c>
+      <c r="S5" s="33"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="32">
+        <v>0</v>
+      </c>
+      <c r="V5" s="33"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="32">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="33"/>
+      <c r="AI5" s="34"/>
+      <c r="AJ5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="33"/>
+      <c r="AL5" s="34"/>
+      <c r="AM5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="33"/>
+      <c r="AO5" s="34"/>
+      <c r="AP5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="33"/>
+      <c r="AR5" s="34"/>
     </row>
     <row r="6" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="39"/>
-      <c r="AB6" s="40"/>
-      <c r="AC6" s="41"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="40"/>
-      <c r="AI6" s="41"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="40"/>
-      <c r="AL6" s="41"/>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="40"/>
-      <c r="AO6" s="41"/>
-      <c r="AP6" s="39"/>
-      <c r="AQ6" s="40"/>
-      <c r="AR6" s="41"/>
+        <v>31</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="34"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="33"/>
+      <c r="AI6" s="34"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="33"/>
+      <c r="AL6" s="34"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="33"/>
+      <c r="AO6" s="34"/>
+      <c r="AP6" s="32"/>
+      <c r="AQ6" s="33"/>
+      <c r="AR6" s="34"/>
     </row>
     <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="39"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="40"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="40"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="39"/>
-      <c r="AK7" s="40"/>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="41"/>
-      <c r="AP7" s="39"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="41"/>
+        <v>32</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="33"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="33"/>
+      <c r="AI7" s="34"/>
+      <c r="AJ7" s="32"/>
+      <c r="AK7" s="33"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="32"/>
+      <c r="AN7" s="33"/>
+      <c r="AO7" s="34"/>
+      <c r="AP7" s="32"/>
+      <c r="AQ7" s="33"/>
+      <c r="AR7" s="34"/>
     </row>
     <row r="8" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="39"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="E8" s="34"/>
+      <c r="F8" s="32"/>
       <c r="G8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="H8" s="34"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="41"/>
-      <c r="L8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="K8" s="34"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="N8" s="41"/>
-      <c r="O8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="N8" s="34"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="32"/>
       <c r="S8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="T8" s="41"/>
-      <c r="U8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="T8" s="34"/>
+      <c r="U8" s="32"/>
       <c r="V8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="W8" s="41"/>
-      <c r="X8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="W8" s="34"/>
+      <c r="X8" s="32"/>
       <c r="Y8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z8" s="41"/>
-      <c r="AA8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="32"/>
       <c r="AB8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC8" s="41"/>
-      <c r="AD8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="32"/>
       <c r="AE8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF8" s="41"/>
-      <c r="AG8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="32"/>
       <c r="AH8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI8" s="41"/>
-      <c r="AJ8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="AI8" s="34"/>
+      <c r="AJ8" s="32"/>
       <c r="AK8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AL8" s="41"/>
-      <c r="AM8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="AL8" s="34"/>
+      <c r="AM8" s="32"/>
       <c r="AN8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AO8" s="41"/>
-      <c r="AP8" s="39"/>
+        <v>29</v>
+      </c>
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="32"/>
       <c r="AQ8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AR8" s="41"/>
+        <v>29</v>
+      </c>
+      <c r="AR8" s="34"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="40"/>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="39"/>
-      <c r="AH9" s="40"/>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="39"/>
-      <c r="AK9" s="40"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="39"/>
-      <c r="AN9" s="40"/>
-      <c r="AO9" s="41"/>
-      <c r="AP9" s="39"/>
-      <c r="AQ9" s="40"/>
-      <c r="AR9" s="41"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="33"/>
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="34"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="33"/>
+      <c r="AI9" s="34"/>
+      <c r="AJ9" s="32"/>
+      <c r="AK9" s="33"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="32"/>
+      <c r="AN9" s="33"/>
+      <c r="AO9" s="34"/>
+      <c r="AP9" s="32"/>
+      <c r="AQ9" s="33"/>
+      <c r="AR9" s="34"/>
     </row>
     <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="40"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="39"/>
-      <c r="AB10" s="40"/>
-      <c r="AC10" s="41"/>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="40"/>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="40"/>
-      <c r="AI10" s="41"/>
-      <c r="AJ10" s="39"/>
-      <c r="AK10" s="40"/>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="39"/>
-      <c r="AN10" s="40"/>
-      <c r="AO10" s="41"/>
-      <c r="AP10" s="39"/>
-      <c r="AQ10" s="40"/>
-      <c r="AR10" s="41"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="34"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="34"/>
+      <c r="AD10" s="32"/>
+      <c r="AE10" s="33"/>
+      <c r="AF10" s="34"/>
+      <c r="AG10" s="32"/>
+      <c r="AH10" s="33"/>
+      <c r="AI10" s="34"/>
+      <c r="AJ10" s="32"/>
+      <c r="AK10" s="33"/>
+      <c r="AL10" s="34"/>
+      <c r="AM10" s="32"/>
+      <c r="AN10" s="33"/>
+      <c r="AO10" s="34"/>
+      <c r="AP10" s="32"/>
+      <c r="AQ10" s="33"/>
+      <c r="AR10" s="34"/>
     </row>
     <row r="11" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="41"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="41"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="41"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="41"/>
-      <c r="AJ11" s="39"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="41"/>
-      <c r="AM11" s="39"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="41"/>
-      <c r="AP11" s="39"/>
-      <c r="AQ11" s="40"/>
-      <c r="AR11" s="41"/>
+        <v>33</v>
+      </c>
+      <c r="C11" s="32"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="34"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="32"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="34"/>
+      <c r="AD11" s="32"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="34"/>
+      <c r="AG11" s="32"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="34"/>
+      <c r="AJ11" s="32"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="34"/>
+      <c r="AM11" s="32"/>
+      <c r="AN11" s="33"/>
+      <c r="AO11" s="34"/>
+      <c r="AP11" s="32"/>
+      <c r="AQ11" s="33"/>
+      <c r="AR11" s="34"/>
     </row>
     <row r="12" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B12" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="40"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="40"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="40"/>
-      <c r="AF12" s="41"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="40"/>
-      <c r="AI12" s="41"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="40"/>
-      <c r="AL12" s="41"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="40"/>
-      <c r="AO12" s="41"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="40"/>
-      <c r="AR12" s="41"/>
+        <v>34</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="34"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="34"/>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="34"/>
+      <c r="AD12" s="32"/>
+      <c r="AE12" s="33"/>
+      <c r="AF12" s="34"/>
+      <c r="AG12" s="32"/>
+      <c r="AH12" s="33"/>
+      <c r="AI12" s="34"/>
+      <c r="AJ12" s="32"/>
+      <c r="AK12" s="33"/>
+      <c r="AL12" s="34"/>
+      <c r="AM12" s="32"/>
+      <c r="AN12" s="33"/>
+      <c r="AO12" s="34"/>
+      <c r="AP12" s="32"/>
+      <c r="AQ12" s="33"/>
+      <c r="AR12" s="34"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B13" s="42"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="45"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="44"/>
-      <c r="W13" s="45"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="44"/>
-      <c r="Z13" s="45"/>
-      <c r="AA13" s="43"/>
-      <c r="AB13" s="44"/>
-      <c r="AC13" s="45"/>
-      <c r="AD13" s="43"/>
-      <c r="AE13" s="44"/>
-      <c r="AF13" s="45"/>
-      <c r="AG13" s="43"/>
-      <c r="AH13" s="44"/>
-      <c r="AI13" s="45"/>
-      <c r="AJ13" s="43"/>
-      <c r="AK13" s="44"/>
-      <c r="AL13" s="45"/>
-      <c r="AM13" s="43"/>
-      <c r="AN13" s="44"/>
-      <c r="AO13" s="45"/>
-      <c r="AP13" s="43"/>
-      <c r="AQ13" s="44"/>
-      <c r="AR13" s="45"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="37"/>
+      <c r="Z13" s="38"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="37"/>
+      <c r="AC13" s="38"/>
+      <c r="AD13" s="36"/>
+      <c r="AE13" s="37"/>
+      <c r="AF13" s="38"/>
+      <c r="AG13" s="36"/>
+      <c r="AH13" s="37"/>
+      <c r="AI13" s="38"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="37"/>
+      <c r="AL13" s="38"/>
+      <c r="AM13" s="36"/>
+      <c r="AN13" s="37"/>
+      <c r="AO13" s="38"/>
+      <c r="AP13" s="36"/>
+      <c r="AQ13" s="37"/>
+      <c r="AR13" s="38"/>
     </row>
     <row r="14" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="46">
         <f>AVERAGE(C4:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="47"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="47">
+      <c r="D14" s="46"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="46">
         <f>AVERAGE(F4:F13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="47"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="47">
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="46">
         <f>AVERAGE(I4:I13)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="47"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="47">
+      <c r="J14" s="46"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="46">
         <f>AVERAGE(L4:L13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="47"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="47">
+      <c r="M14" s="46"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="46">
         <f>AVERAGE(O4:O13)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="48"/>
-      <c r="R14" s="47">
+      <c r="P14" s="46"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="46">
         <f>AVERAGE(R4:R13)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="47"/>
-      <c r="T14" s="48"/>
-      <c r="U14" s="47">
+      <c r="S14" s="46"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="46">
         <f>AVERAGE(U4:U13)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="47"/>
-      <c r="W14" s="48"/>
-      <c r="X14" s="47">
+      <c r="V14" s="46"/>
+      <c r="W14" s="47"/>
+      <c r="X14" s="46">
         <f>AVERAGE(X4:X13)</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="48"/>
-      <c r="AA14" s="47">
+      <c r="Y14" s="46"/>
+      <c r="Z14" s="47"/>
+      <c r="AA14" s="46">
         <f>AVERAGE(AA4:AA13)</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="47"/>
-      <c r="AC14" s="48"/>
-      <c r="AD14" s="47">
+      <c r="AB14" s="46"/>
+      <c r="AC14" s="47"/>
+      <c r="AD14" s="46">
         <f>AVERAGE(AD4:AD13)</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="47"/>
-      <c r="AF14" s="48"/>
-      <c r="AG14" s="47">
+      <c r="AE14" s="46"/>
+      <c r="AF14" s="47"/>
+      <c r="AG14" s="46">
         <f>AVERAGE(AG4:AG13)</f>
         <v>0</v>
       </c>
-      <c r="AH14" s="47"/>
-      <c r="AI14" s="48"/>
-      <c r="AJ14" s="47">
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="47"/>
+      <c r="AJ14" s="46">
         <f>AVERAGE(AJ4:AJ13)</f>
         <v>0</v>
       </c>
-      <c r="AK14" s="47"/>
-      <c r="AL14" s="48"/>
-      <c r="AM14" s="47">
+      <c r="AK14" s="46"/>
+      <c r="AL14" s="47"/>
+      <c r="AM14" s="46">
         <f>AVERAGE(AM4:AM13)</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="47"/>
-      <c r="AO14" s="48"/>
-      <c r="AP14" s="47">
+      <c r="AN14" s="46"/>
+      <c r="AO14" s="47"/>
+      <c r="AP14" s="46">
         <f>AVERAGE(AP4:AP13)</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="47"/>
-      <c r="AR14" s="48"/>
+      <c r="AQ14" s="46"/>
+      <c r="AR14" s="47"/>
     </row>
     <row r="15" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="17"/>
@@ -4902,6 +4895,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="AM14:AO14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="AA14:AC14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AJ14:AL14"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP14:AR14"/>
@@ -4918,19 +4924,6 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="AM14:AO14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="AA14:AC14"/>
-    <mergeCell ref="AD14:AF14"/>
-    <mergeCell ref="AG14:AI14"/>
-    <mergeCell ref="AJ14:AL14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A09/M01A09_TaludRef.xlsx
+++ b/activity/M01A09/M01A09_TaludRef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F526E-5364-4C44-A4DF-B38D2C619A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFE3704-5F44-4A9B-92D8-B6ECABEC9EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -582,12 +582,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -626,6 +620,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -647,8 +644,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -754,11 +754,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calificacion!$D$4</c:f>
+              <c:f>Calificacion!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Calificación Instructor</c:v>
+                  <c:v>Calificación final</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -784,13 +784,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -802,7 +802,6 @@
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inBase"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -812,7 +811,21 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -841,7 +854,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calificacion!$D$5:$D$9</c:f>
+              <c:f>Calificacion!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1705,15 +1718,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>16010</xdr:colOff>
+      <xdr:colOff>75541</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>60431</xdr:rowOff>
+      <xdr:rowOff>173540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>66964</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>160157</xdr:rowOff>
+      <xdr:colOff>126495</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76813</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2059,20 +2072,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
@@ -2095,14 +2108,14 @@
       <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="47">
         <v>5</v>
       </c>
       <c r="D5" s="22">
         <f>Detalle!C14*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="24">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2112,14 +2125,14 @@
       <c r="B6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="47">
         <v>5</v>
       </c>
       <c r="D6" s="22">
         <f>Detalle!F14*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="24">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2129,14 +2142,14 @@
       <c r="B7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="47">
         <v>5</v>
       </c>
       <c r="D7" s="22">
         <f>Detalle!I14*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2146,14 +2159,14 @@
       <c r="B8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="47">
         <v>5</v>
       </c>
       <c r="D8" s="22">
         <f>Detalle!L14*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="30"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2163,14 +2176,14 @@
       <c r="B9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="47">
         <v>5</v>
       </c>
       <c r="D9" s="22">
         <f>Detalle!O14*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="30"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2180,14 +2193,14 @@
       <c r="B10" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="47">
         <v>5</v>
       </c>
       <c r="D10" s="22">
         <f>Detalle!R14*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="30"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2197,14 +2210,14 @@
       <c r="B11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="47">
         <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>Detalle!U14*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="30"/>
+      <c r="E11" s="28"/>
       <c r="F11" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2214,14 +2227,14 @@
       <c r="B12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="47">
         <v>5</v>
       </c>
       <c r="D12" s="22">
         <f>Detalle!X14*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="30"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2231,14 +2244,14 @@
       <c r="B13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="47">
         <v>5</v>
       </c>
       <c r="D13" s="22">
         <f>Detalle!AA14*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2248,14 +2261,14 @@
       <c r="B14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="47">
         <v>5</v>
       </c>
       <c r="D14" s="22">
         <f>Detalle!AD14*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="30"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2265,14 +2278,14 @@
       <c r="B15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="47">
         <v>5</v>
       </c>
       <c r="D15" s="22">
         <f>Detalle!AG14*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="30"/>
+      <c r="E15" s="28"/>
       <c r="F15" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2282,14 +2295,14 @@
       <c r="B16" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="47">
         <v>5</v>
       </c>
       <c r="D16" s="22">
         <f>Detalle!AJ14*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="30"/>
+      <c r="E16" s="28"/>
       <c r="F16" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2299,14 +2312,14 @@
       <c r="B17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="47">
         <v>5</v>
       </c>
       <c r="D17" s="22">
         <f>Detalle!AM14*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="30"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2316,35 +2329,35 @@
       <c r="B18" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="48">
         <v>5</v>
       </c>
       <c r="D18" s="23">
         <f>Detalle!AP14*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="31"/>
+      <c r="E18" s="29"/>
       <c r="F18" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="48" t="str">
+      <c r="B19" s="39" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A09 en GitHub.</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="27"/>
@@ -2442,96 +2455,96 @@
     </row>
     <row r="2" spans="1:44" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="43" t="str">
+      <c r="C2" s="42" t="str">
         <f>Calificacion!B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="43" t="str">
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="42" t="str">
         <f>Calificacion!B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="43" t="str">
+      <c r="G2" s="43"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="42" t="str">
         <f>Calificacion!B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="44"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="43" t="str">
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="42" t="str">
         <f>Calificacion!B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="43" t="str">
+      <c r="M2" s="43"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="42" t="str">
         <f>Calificacion!B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="43" t="str">
+      <c r="P2" s="43"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="42" t="str">
         <f>Calificacion!B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="44"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="43" t="str">
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="42" t="str">
         <f>Calificacion!B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="44"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="43" t="str">
+      <c r="V2" s="43"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="42" t="str">
         <f>Calificacion!B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="43" t="str">
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="42" t="str">
         <f>Calificacion!B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="43" t="str">
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="42" t="str">
         <f>Calificacion!B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="43" t="str">
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="42" t="str">
         <f>Calificacion!B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="43" t="str">
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="42" t="str">
         <f>Calificacion!B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="44"/>
-      <c r="AL2" s="45"/>
-      <c r="AM2" s="43" t="str">
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="42" t="str">
         <f>Calificacion!B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="43" t="str">
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="42" t="str">
         <f>Calificacion!B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="45"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="44"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="42"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2663,615 +2676,615 @@
       <c r="B4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="32"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="33"/>
-      <c r="AI4" s="34"/>
-      <c r="AJ4" s="32"/>
-      <c r="AK4" s="33"/>
-      <c r="AL4" s="34"/>
-      <c r="AM4" s="32"/>
-      <c r="AN4" s="33"/>
-      <c r="AO4" s="34"/>
-      <c r="AP4" s="32"/>
-      <c r="AQ4" s="33"/>
-      <c r="AR4" s="34"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="31"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="31"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="30"/>
+      <c r="AN4" s="31"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="30"/>
+      <c r="AQ4" s="31"/>
+      <c r="AR4" s="32"/>
     </row>
     <row r="5" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="32">
-        <v>0</v>
-      </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="32">
-        <v>0</v>
-      </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="32">
-        <v>0</v>
-      </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="32">
-        <v>0</v>
-      </c>
-      <c r="M5" s="33"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="32">
-        <v>0</v>
-      </c>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="32">
-        <v>0</v>
-      </c>
-      <c r="S5" s="33"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="32">
-        <v>0</v>
-      </c>
-      <c r="V5" s="33"/>
-      <c r="W5" s="34"/>
-      <c r="X5" s="32">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="34"/>
-      <c r="AA5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="34"/>
-      <c r="AD5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="33"/>
-      <c r="AF5" s="34"/>
-      <c r="AG5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="33"/>
-      <c r="AI5" s="34"/>
-      <c r="AJ5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="33"/>
-      <c r="AL5" s="34"/>
-      <c r="AM5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="33"/>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="33"/>
-      <c r="AR5" s="34"/>
+      <c r="C5" s="30">
+        <v>0</v>
+      </c>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="30">
+        <v>0</v>
+      </c>
+      <c r="G5" s="31"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="30">
+        <v>0</v>
+      </c>
+      <c r="J5" s="31"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="30">
+        <v>0</v>
+      </c>
+      <c r="M5" s="31"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="30">
+        <v>0</v>
+      </c>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="30">
+        <v>0</v>
+      </c>
+      <c r="S5" s="31"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="30">
+        <v>0</v>
+      </c>
+      <c r="V5" s="31"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="32"/>
+      <c r="AJ5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="32"/>
+      <c r="AP5" s="30">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="32"/>
     </row>
     <row r="6" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="34"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="34"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="34"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="34"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="34"/>
-      <c r="AJ6" s="32"/>
-      <c r="AK6" s="33"/>
-      <c r="AL6" s="34"/>
-      <c r="AM6" s="32"/>
-      <c r="AN6" s="33"/>
-      <c r="AO6" s="34"/>
-      <c r="AP6" s="32"/>
-      <c r="AQ6" s="33"/>
-      <c r="AR6" s="34"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="32"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="31"/>
+      <c r="AL6" s="32"/>
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="31"/>
+      <c r="AO6" s="32"/>
+      <c r="AP6" s="30"/>
+      <c r="AQ6" s="31"/>
+      <c r="AR6" s="32"/>
     </row>
     <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="32"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="34"/>
-      <c r="X7" s="32"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="34"/>
-      <c r="AA7" s="32"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="34"/>
-      <c r="AD7" s="32"/>
-      <c r="AE7" s="33"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="32"/>
-      <c r="AH7" s="33"/>
-      <c r="AI7" s="34"/>
-      <c r="AJ7" s="32"/>
-      <c r="AK7" s="33"/>
-      <c r="AL7" s="34"/>
-      <c r="AM7" s="32"/>
-      <c r="AN7" s="33"/>
-      <c r="AO7" s="34"/>
-      <c r="AP7" s="32"/>
-      <c r="AQ7" s="33"/>
-      <c r="AR7" s="34"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="32"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="31"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="32"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="32"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="31"/>
+      <c r="AL7" s="32"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="31"/>
+      <c r="AO7" s="32"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="31"/>
+      <c r="AR7" s="32"/>
     </row>
     <row r="8" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="32"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
       <c r="G8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="30"/>
       <c r="J8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="34"/>
-      <c r="L8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="30"/>
       <c r="M8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="30"/>
       <c r="P8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="30"/>
       <c r="S8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="T8" s="34"/>
-      <c r="U8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="30"/>
       <c r="V8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="W8" s="34"/>
-      <c r="X8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="30"/>
       <c r="Y8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Z8" s="34"/>
-      <c r="AA8" s="32"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="30"/>
       <c r="AB8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="32"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="30"/>
       <c r="AE8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="32"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="30"/>
       <c r="AH8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="32"/>
+      <c r="AI8" s="32"/>
+      <c r="AJ8" s="30"/>
       <c r="AK8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AL8" s="34"/>
-      <c r="AM8" s="32"/>
+      <c r="AL8" s="32"/>
+      <c r="AM8" s="30"/>
       <c r="AN8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="32"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="30"/>
       <c r="AQ8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AR8" s="34"/>
+      <c r="AR8" s="32"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="32"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="32"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="33"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="32"/>
-      <c r="AH9" s="33"/>
-      <c r="AI9" s="34"/>
-      <c r="AJ9" s="32"/>
-      <c r="AK9" s="33"/>
-      <c r="AL9" s="34"/>
-      <c r="AM9" s="32"/>
-      <c r="AN9" s="33"/>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="32"/>
-      <c r="AQ9" s="33"/>
-      <c r="AR9" s="34"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="32"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="31"/>
+      <c r="AI9" s="32"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="31"/>
+      <c r="AL9" s="32"/>
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="31"/>
+      <c r="AO9" s="32"/>
+      <c r="AP9" s="30"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="32"/>
     </row>
     <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="32"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="34"/>
-      <c r="AA10" s="32"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="34"/>
-      <c r="AD10" s="32"/>
-      <c r="AE10" s="33"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="32"/>
-      <c r="AH10" s="33"/>
-      <c r="AI10" s="34"/>
-      <c r="AJ10" s="32"/>
-      <c r="AK10" s="33"/>
-      <c r="AL10" s="34"/>
-      <c r="AM10" s="32"/>
-      <c r="AN10" s="33"/>
-      <c r="AO10" s="34"/>
-      <c r="AP10" s="32"/>
-      <c r="AQ10" s="33"/>
-      <c r="AR10" s="34"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="32"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="32"/>
+      <c r="AJ10" s="30"/>
+      <c r="AK10" s="31"/>
+      <c r="AL10" s="32"/>
+      <c r="AM10" s="30"/>
+      <c r="AN10" s="31"/>
+      <c r="AO10" s="32"/>
+      <c r="AP10" s="30"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="32"/>
     </row>
     <row r="11" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="32"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="32"/>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="34"/>
-      <c r="AA11" s="32"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="34"/>
-      <c r="AD11" s="32"/>
-      <c r="AE11" s="33"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="32"/>
-      <c r="AH11" s="33"/>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="32"/>
-      <c r="AK11" s="33"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="32"/>
-      <c r="AN11" s="33"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="32"/>
-      <c r="AQ11" s="33"/>
-      <c r="AR11" s="34"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="32"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="32"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="32"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="32"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="32"/>
+      <c r="AJ11" s="30"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="32"/>
+      <c r="AM11" s="30"/>
+      <c r="AN11" s="31"/>
+      <c r="AO11" s="32"/>
+      <c r="AP11" s="30"/>
+      <c r="AQ11" s="31"/>
+      <c r="AR11" s="32"/>
     </row>
     <row r="12" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="32"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="32"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="34"/>
-      <c r="X12" s="32"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="34"/>
-      <c r="AA12" s="32"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="34"/>
-      <c r="AD12" s="32"/>
-      <c r="AE12" s="33"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="32"/>
-      <c r="AH12" s="33"/>
-      <c r="AI12" s="34"/>
-      <c r="AJ12" s="32"/>
-      <c r="AK12" s="33"/>
-      <c r="AL12" s="34"/>
-      <c r="AM12" s="32"/>
-      <c r="AN12" s="33"/>
-      <c r="AO12" s="34"/>
-      <c r="AP12" s="32"/>
-      <c r="AQ12" s="33"/>
-      <c r="AR12" s="34"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="32"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="32"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="32"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="32"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="32"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="32"/>
+      <c r="AM12" s="30"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="32"/>
+      <c r="AP12" s="30"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="32"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="38"/>
-      <c r="AD13" s="36"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="38"/>
-      <c r="AG13" s="36"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="38"/>
-      <c r="AJ13" s="36"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="38"/>
-      <c r="AM13" s="36"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="38"/>
-      <c r="AP13" s="36"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="38"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="34"/>
+      <c r="AE13" s="35"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="34"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="34"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="34"/>
+      <c r="AN13" s="35"/>
+      <c r="AO13" s="36"/>
+      <c r="AP13" s="34"/>
+      <c r="AQ13" s="35"/>
+      <c r="AR13" s="36"/>
     </row>
     <row r="14" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="45">
         <f>AVERAGE(C4:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="46">
+      <c r="D14" s="45"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="45">
         <f>AVERAGE(F4:F13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="46">
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="45">
         <f>AVERAGE(I4:I13)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="46"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="46">
+      <c r="J14" s="45"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="45">
         <f>AVERAGE(L4:L13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="46"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="46">
+      <c r="M14" s="45"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="45">
         <f>AVERAGE(O4:O13)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="46">
+      <c r="P14" s="45"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="45">
         <f>AVERAGE(R4:R13)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="46"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="46">
+      <c r="S14" s="45"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="45">
         <f>AVERAGE(U4:U13)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="46"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="46">
+      <c r="V14" s="45"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="45">
         <f>AVERAGE(X4:X13)</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="46"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="46">
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="46"/>
+      <c r="AA14" s="45">
         <f>AVERAGE(AA4:AA13)</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="46"/>
-      <c r="AC14" s="47"/>
-      <c r="AD14" s="46">
+      <c r="AB14" s="45"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="45">
         <f>AVERAGE(AD4:AD13)</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="46"/>
-      <c r="AF14" s="47"/>
-      <c r="AG14" s="46">
+      <c r="AE14" s="45"/>
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="45">
         <f>AVERAGE(AG4:AG13)</f>
         <v>0</v>
       </c>
-      <c r="AH14" s="46"/>
-      <c r="AI14" s="47"/>
-      <c r="AJ14" s="46">
+      <c r="AH14" s="45"/>
+      <c r="AI14" s="46"/>
+      <c r="AJ14" s="45">
         <f>AVERAGE(AJ4:AJ13)</f>
         <v>0</v>
       </c>
-      <c r="AK14" s="46"/>
-      <c r="AL14" s="47"/>
-      <c r="AM14" s="46">
+      <c r="AK14" s="45"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="45">
         <f>AVERAGE(AM4:AM13)</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="46"/>
-      <c r="AO14" s="47"/>
-      <c r="AP14" s="46">
+      <c r="AN14" s="45"/>
+      <c r="AO14" s="46"/>
+      <c r="AP14" s="45">
         <f>AVERAGE(AP4:AP13)</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="46"/>
-      <c r="AR14" s="47"/>
+      <c r="AQ14" s="45"/>
+      <c r="AR14" s="46"/>
     </row>
     <row r="15" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="17"/>
